--- a/Planilha RGA(base).xlsx
+++ b/Planilha RGA(base).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denes.tavares\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7064FE5-49F4-4674-9B83-90FABAFBC201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB61EEDB-C78B-49B3-9F71-2EEFBC9110FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,6 +31,12 @@
     <t>POLARIDADE</t>
   </si>
   <si>
+    <t>INDICADOR DA META GERAL</t>
+  </si>
+  <si>
+    <t>FONTE DOS DADOS</t>
+  </si>
+  <si>
     <t>META GERAL FOI MONITORADA UTILIZANDO DADOS DO SINESP?</t>
   </si>
   <si>
@@ -40,7 +46,7 @@
     <t>VALOR DE REFERÊNCIA (MONITORADO NO EXERCÍCIO FINANCEIRO EM ANÁLISE)</t>
   </si>
   <si>
-    <t>VALOR/ALCANCE DA META GERAL NO EXERCÍCIO EM ANÁLISE (%)</t>
+    <t>RESULTADO ALCANÇADO DA META GERAL</t>
   </si>
   <si>
     <t>DESCRIÇÃO DA META ESPECÍFICA</t>
@@ -49,35 +55,29 @@
     <t>BENS E/OU SERVIÇOS ADQUIRIDOS</t>
   </si>
   <si>
+    <t>A AQUISIÇÃO/CONTRATAÇÃO FOI PREVISTA EM PLANO DE APLICAÇÃO?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HÁ VEDAÇÃO EXPRESSA DO ITEM ADQUIRIDO? </t>
+  </si>
+  <si>
     <t>INDICADOR DA META ESPECÍFICA</t>
   </si>
   <si>
-    <t>FONTE DOS DADOS</t>
+    <t>VALOR/ALCANCE DA META ESPECÍFICA NO EXERCÍCIO EM ANÁLISE (%)</t>
   </si>
   <si>
     <t>RESULTADO ALCANÇADO</t>
   </si>
   <si>
-    <t>INDICADOR DA META GERAL</t>
-  </si>
-  <si>
-    <t>RESULTADO ALCANÇADO DA META GERAL</t>
-  </si>
-  <si>
-    <t>A AQUISIÇÃO/CONTRATAÇÃO FOI PREVISTA EM PLANO DE APLICAÇÃO?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HÁ VEDAÇÃO EXPRESSA DO ITEM ADQUIRIDO? </t>
-  </si>
-  <si>
-    <t>VALOR/ALCANCE DA META ESPECÍFICA NO EXERCÍCIO EM ANÁLISE (%)</t>
+    <t>VALOR/AILCANCE DA META GERAL NO EXERCÍCIO EM ANÁLISE (%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,8 +104,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,12 +132,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -143,6 +145,19 @@
       <left style="double">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF000000"/>
+      </left>
       <right style="double">
         <color rgb="FF000000"/>
       </right>
@@ -163,28 +178,6 @@
       <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -207,51 +200,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
@@ -570,71 +569,71 @@
     <col min="11" max="11" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
     </row>
-    <row r="2" spans="1:13" ht="75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>13</v>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="226.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+    <row r="3" spans="1:11" ht="226.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
@@ -648,77 +647,72 @@
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="13"/>
     </row>
-    <row r="6" spans="1:13" ht="55.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
     </row>
-    <row r="7" spans="1:13" ht="257.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="14"/>
+    <row r="7" spans="1:11" ht="257.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:13" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+    <row r="8" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="H7:K7"/>
     <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Planilha RGA(base).xlsx
+++ b/Planilha RGA(base).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denes.tavares\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB61EEDB-C78B-49B3-9F71-2EEFBC9110FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EB4F2A-A75B-4EA4-A006-71B1E92C356F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -200,24 +200,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -235,22 +222,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,23 +556,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:11" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -648,11 +634,11 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
     </row>
-    <row r="6" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:11" ht="55.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -661,7 +647,7 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -683,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="257.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="257.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -691,10 +677,10 @@
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
@@ -710,9 +696,8 @@
       <c r="K8" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="H7:K7"/>
     <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Planilha RGA(base).xlsx
+++ b/Planilha RGA(base).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denes.tavares\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EB4F2A-A75B-4EA4-A006-71B1E92C356F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884453C4-F039-477A-9D5C-CD1A1151FA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -204,14 +204,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -233,10 +230,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,23 +555,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:11" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:11" ht="110.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -597,48 +596,48 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="226.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+    <row r="3" spans="1:11" ht="226.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
+    <row r="4" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" ht="55.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -647,7 +646,7 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -670,30 +669,30 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="257.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Planilha RGA(base).xlsx
+++ b/Planilha RGA(base).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denes.tavares\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884453C4-F039-477A-9D5C-CD1A1151FA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB15241-671F-4002-9281-CE69C9890A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,6 +222,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -231,10 +234,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,17 +555,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:11" ht="110.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -597,7 +597,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="226.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
+      <c r="A3" s="12"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -619,19 +619,19 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:11" ht="55.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -669,7 +669,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="257.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -677,9 +677,9 @@
       <c r="F7" s="3"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
